--- a/data/inflationbenelux.xlsx
+++ b/data/inflationbenelux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC229BDA-096D-4863-A6FD-A47B76E4A64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB44A98B-4AC3-43C0-9BB4-676BFD3ED3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{1ECD916D-2A88-4086-A074-28AAEBE869C7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Belgium</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>2.54%</t>
+  </si>
+  <si>
+    <t>Country</t>
   </si>
 </sst>
 </file>
@@ -536,6 +539,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="B1">
         <v>2014</v>
       </c>

--- a/data/inflationbenelux.xlsx
+++ b/data/inflationbenelux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB44A98B-4AC3-43C0-9BB4-676BFD3ED3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85363208-4197-4C08-8AF0-23855A3973E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{1ECD916D-2A88-4086-A074-28AAEBE869C7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>Belgium</t>
   </si>
@@ -47,109 +47,94 @@
     <t>Luxembourg</t>
   </si>
   <si>
-    <t>-0.39%</t>
-  </si>
-  <si>
-    <t>1.45%</t>
-  </si>
-  <si>
-    <t>2.20%</t>
-  </si>
-  <si>
-    <t>2.06%</t>
-  </si>
-  <si>
-    <t>0.92%</t>
-  </si>
-  <si>
-    <t>0.35%</t>
-  </si>
-  <si>
-    <t>6.59%</t>
-  </si>
-  <si>
-    <t>10.21%</t>
-  </si>
-  <si>
-    <t>0.53%</t>
-  </si>
-  <si>
-    <t>4.41%</t>
-  </si>
-  <si>
-    <t>-0.14%</t>
-  </si>
-  <si>
-    <t>0.45%</t>
-  </si>
-  <si>
-    <t>0.75%</t>
-  </si>
-  <si>
-    <t>1.21%</t>
-  </si>
-  <si>
-    <t>1.79%</t>
-  </si>
-  <si>
-    <t>2.70%</t>
-  </si>
-  <si>
-    <t>0.88%</t>
-  </si>
-  <si>
-    <t>6.45%</t>
-  </si>
-  <si>
-    <t>11.14%</t>
-  </si>
-  <si>
-    <t>1.13%</t>
-  </si>
-  <si>
-    <t>4.03%</t>
-  </si>
-  <si>
-    <t>-1.00%</t>
-  </si>
-  <si>
-    <t>0.81%</t>
-  </si>
-  <si>
-    <t>1.55%</t>
-  </si>
-  <si>
-    <t>1.57%</t>
-  </si>
-  <si>
-    <t>1.95%</t>
-  </si>
-  <si>
-    <t>-0.16%</t>
-  </si>
-  <si>
-    <t>5.64%</t>
-  </si>
-  <si>
-    <t>6.37%</t>
-  </si>
-  <si>
-    <t>3.26%</t>
-  </si>
-  <si>
-    <t>1.65%</t>
-  </si>
-  <si>
-    <t>3.30%</t>
-  </si>
-  <si>
-    <t>3.00%</t>
-  </si>
-  <si>
-    <t>2.54%</t>
-  </si>
-  <si>
     <t>Country</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>11.6%</t>
+  </si>
+  <si>
+    <t>4.1%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
   </si>
 </sst>
 </file>
@@ -193,11 +178,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,7 +527,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>2014</v>
@@ -584,28 +571,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
@@ -617,7 +604,7 @@
         <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -634,31 +621,31 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -669,37 +656,37 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>30</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" t="s">
         <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
